--- a/组合实盘追踪/20260520_银河.xlsx
+++ b/组合实盘追踪/20260520_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>703.4</v>
+        <v>709</v>
       </c>
       <c r="D2" s="1">
-        <v>-5</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0071</v>
+        <v>0.0008</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0108</v>
+        <v>-0.003</v>
       </c>
       <c r="L2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0108</v>
+        <v>-0.003</v>
       </c>
       <c r="N2" s="1">
-        <v>2.2</v>
+        <v>11.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-7.7</v>
+        <v>-2.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0238</v>
+        <v>0.024</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>8</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0071</v>
+        <v>0.0008</v>
       </c>
       <c r="U2" s="5">
-        <v>3.517</v>
+        <v>3.545</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0111</v>
+        <v>0.0031</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0562</v>
+        <v>0.0646</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0706</v>
+        <v>0.0791</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1901</v>
+        <v>0.1996</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4575</v>
+        <v>0.4691</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>848</v>
+        <v>841.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.8</v>
+        <v>-7.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0009</v>
+        <v>-0.009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0173</v>
+        <v>-0.0252</v>
       </c>
       <c r="L3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0173</v>
+        <v>-0.0252</v>
       </c>
       <c r="N3" s="1">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="O3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="P3" s="1">
-        <v>-14.9</v>
+        <v>-21.7</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0287</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>8</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0009</v>
+        <v>-0.009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.12</v>
+        <v>2.103</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0175</v>
+        <v>0.0257</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0124</v>
+        <v>0.0043</v>
       </c>
       <c r="Y3" s="2">
+        <v>0.0515</v>
+      </c>
+      <c r="Z3" s="2">
         <v>0.06</v>
       </c>
-      <c r="Z3" s="2">
-        <v>0.0686</v>
-      </c>
       <c r="AA3" s="2">
-        <v>0.1169</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>699.6</v>
+        <v>704</v>
       </c>
       <c r="D4" s="1">
-        <v>-3.3</v>
+        <v>1.1</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0047</v>
+        <v>0.0016</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0509</v>
+        <v>-0.0449</v>
       </c>
       <c r="L4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0509</v>
+        <v>-0.0449</v>
       </c>
       <c r="N4" s="1">
-        <v>-20.9</v>
+        <v>-9.9</v>
       </c>
       <c r="O4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="P4" s="1">
-        <v>-37.5</v>
+        <v>-33.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0237</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>8</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0047</v>
+        <v>0.0016</v>
       </c>
       <c r="U4" s="5">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0535</v>
+        <v>0.0469</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0392</v>
+        <v>-0.0332</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1203</v>
+        <v>-0.1148</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1783</v>
+        <v>-0.1731</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1276</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>969</v>
+        <v>974.2</v>
       </c>
       <c r="D5" s="1">
-        <v>-4.8</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0049</v>
+        <v>0.0004</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="L5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="N5" s="1">
-        <v>-10.4</v>
+        <v>-1.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="P5" s="1">
-        <v>-22.3</v>
+        <v>-17.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0328</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>8</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0049</v>
+        <v>0.0004</v>
       </c>
       <c r="U5" s="5">
-        <v>4.845</v>
+        <v>4.871</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0231</v>
+        <v>0.0177</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0223</v>
+        <v>0.0278</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0373</v>
+        <v>0.0428</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0583</v>
+        <v>0.0639</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2762</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940</v>
+        <v>936.7</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.5</v>
+        <v>-14.8</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0121</v>
+        <v>-0.0156</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0346</v>
+        <v>-0.038</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0346</v>
+        <v>-0.038</v>
       </c>
       <c r="N6" s="1">
-        <v>-23.8</v>
+        <v>-18.7</v>
       </c>
       <c r="O6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="P6" s="1">
-        <v>-33.7</v>
+        <v>-37</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0318</v>
@@ -915,28 +915,28 @@
         <v>8</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0121</v>
+        <v>-0.0156</v>
       </c>
       <c r="U6" s="5">
-        <v>9.4</v>
+        <v>9.367</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0359</v>
+        <v>0.0395</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0628</v>
+        <v>-0.0661</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1111</v>
+        <v>-0.1142</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0499</v>
+        <v>0.0462</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3016</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="7">
@@ -947,46 +947,46 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3024</v>
+        <v>3018.6</v>
       </c>
       <c r="D7" s="1">
+        <v>-5.4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-0.0018</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="L7" s="1">
+        <v>-0.15</v>
+      </c>
+      <c r="M7" s="2">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0017</v>
-      </c>
-      <c r="L7" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0017</v>
-      </c>
       <c r="N7" s="1">
-        <v>5.4</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>5.25</v>
+        <v>-0.15</v>
       </c>
       <c r="P7" s="1">
-        <v>5.25</v>
+        <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
         <v>0.1024</v>
@@ -998,10 +998,10 @@
         <v>8</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.12</v>
+        <v>1.118</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0027</v>
+        <v>0.0009</v>
       </c>
       <c r="Y7" s="2">
+        <v>0.0072</v>
+      </c>
+      <c r="Z7" s="2">
         <v>0.009</v>
       </c>
-      <c r="Z7" s="2">
-        <v>0.0108</v>
-      </c>
       <c r="AA7" s="2">
-        <v>0.0206</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>779</v>
+        <v>786.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0069</v>
+        <v>0.0025</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0098</v>
+        <v>-0.0004</v>
       </c>
       <c r="L8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0098</v>
+        <v>-0.0004</v>
       </c>
       <c r="N8" s="1">
-        <v>-5.8</v>
+        <v>-7.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-7.7</v>
+        <v>-0.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0267</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>8</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0069</v>
+        <v>0.0025</v>
       </c>
       <c r="U8" s="5">
-        <v>3.895</v>
+        <v>3.932</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.01</v>
+        <v>0.0005</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0613</v>
+        <v>0.0714</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1929</v>
+        <v>0.2043</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2742</v>
+        <v>0.2863</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9455</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20048</v>
+        <v>19985</v>
       </c>
       <c r="D9" s="1">
-        <v>-43.4</v>
+        <v>-106.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0022</v>
+        <v>-0.0053</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0162</v>
+        <v>-0.0193</v>
       </c>
       <c r="L9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0162</v>
+        <v>-0.0193</v>
       </c>
       <c r="N9" s="1">
-        <v>186.2</v>
+        <v>217</v>
       </c>
       <c r="O9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-329.64</v>
+        <v>-392.64</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.679</v>
+        <v>0.6778</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>8</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0022</v>
+        <v>-0.0053</v>
       </c>
       <c r="U9" s="5">
-        <v>14.32</v>
+        <v>14.275</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0164</v>
+        <v>0.0196</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0014</v>
+        <v>-0.0045</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0204</v>
+        <v>-0.0235</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0508</v>
+        <v>0.0475</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1941</v>
+        <v>0.1904</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D10" s="1">
-        <v>2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0036</v>
+        <v>-0.0024</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0061</v>
+        <v>-0.0121</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0061</v>
+        <v>-0.0121</v>
       </c>
       <c r="N10" s="1">
         <v>4.4</v>
       </c>
       <c r="O10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-4.1</v>
+        <v>-8.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0226</v>
+        <v>0.0225</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>8</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0036</v>
+        <v>-0.0024</v>
       </c>
       <c r="U10" s="5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="X10" s="2">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.316</v>
+        <v>0.3081</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3859</v>
+        <v>0.3776</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2748</v>
+        <v>0.2671</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="D11" s="1">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.007</v>
+        <v>0.0047</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0145</v>
+        <v>-0.0029</v>
       </c>
       <c r="L11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0145</v>
+        <v>-0.0029</v>
       </c>
       <c r="N11" s="1">
-        <v>-16</v>
+        <v>5.6</v>
       </c>
       <c r="O11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-12.5</v>
+        <v>-2.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0287</v>
+        <v>0.0291</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>8</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.007</v>
+        <v>0.0047</v>
       </c>
       <c r="U11" s="5">
-        <v>2.12</v>
+        <v>2.145</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0146</v>
+        <v>0.0028</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0019</v>
+        <v>0.0137</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0331</v>
+        <v>0.0453</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1772</v>
+        <v>0.1911</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2672</v>
+        <v>0.2822</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29527</v>
+        <v>29477.1</v>
       </c>
       <c r="D12" s="1">
-        <v>-77.8</v>
+        <v>-127.7</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0026</v>
+        <v>-0.0043</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0155</v>
+        <v>-0.0172</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,16 +1395,16 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>125.3</v>
+        <v>203.7</v>
       </c>
       <c r="O12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-464.79</v>
+        <v>-514.69</v>
       </c>
       <c r="Q12" s="2">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>
